--- a/assets/constructions/examples/ctd_tsmb_face_chamfer.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_face_chamfer.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,44 +614,65 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M410CH45L15R VBX</t>
+          <t>PICCO R 520.0045-15N IC908</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>PICCO R/L 520-N</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VAR_M4R</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>KNSH</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -659,42 +680,38 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>36</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>18.2</v>
+        <v>45</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>45</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>45</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>ISCAR_PICCO:5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -704,12 +721,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>IC908</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -720,7 +737,7 @@
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
@@ -728,7 +745,18 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2020 / ISCAR website</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
@@ -840,40 +868,55 @@
           <t>2020 / ISCAR website</t>
         </is>
       </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PICCO R 520.0045-15N IC908</t>
+          <t>M410CH45L15L VBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PICCO R/L 520-N</t>
+          <t>Microscope</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VAR_M4L</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KNSH</t>
-        </is>
-      </c>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -881,38 +924,42 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>36</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>45</v>
+        <v>18.2</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>45</v>
+      </c>
       <c r="Y4" t="n">
         <v>45</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>ISCAR_PICCO:5</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -922,12 +969,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>IC908</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -938,7 +985,7 @@
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
@@ -946,14 +993,33 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2020 / ISCAR website</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>2960.27</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M410CH45L15L VBX</t>
+          <t>M410CH45L15R VBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -971,7 +1037,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VAR_M4L</t>
+          <t>VAR_M4R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1010,7 +1076,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1064,6 +1130,25 @@
       <c r="AK5" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>2960.27</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
